--- a/data/2025/23-ialomita/92658-slobozia/budget_file.xlsx
+++ b/data/2025/23-ialomita/92658-slobozia/budget_file.xlsx
@@ -7424,7 +7424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7470,12 +7470,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7483,24 +7483,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7509,41 +7504,36 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7553,77 +7543,82 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 34.062.880,00 != sum(children) 41.072.880,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18.00.01</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p3: 0 cells recovered</t>
+          <t>code 18.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -7639,11 +7634,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7653,7 +7648,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11.02 total: parent 34.062.880,00 != sum(children) 41.072.880,00 (1 children)</t>
+          <t>30.02 total: parent 5.000.000,00 != sum(children) 9.892.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7673,12 +7668,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.00.01</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>code 18.00.01 (revenue) not in nomenclator</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -7698,19 +7693,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -7723,19 +7718,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>42.02 total: parent 90.321.901,00 != sum(children) 102.983.315,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -7744,12 +7744,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -7758,7 +7753,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.02 total: parent 5.000.000,00 != sum(children) 9.892.000,00 (1 children)</t>
+          <t>unparseable cell '55.880.503 45.737.620' in column total</t>
         </is>
       </c>
     </row>
@@ -7774,41 +7769,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>code 10.20 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>10.20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>10.20 total: parent 0,00 != sum(children) 26.688.357,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -7824,11 +7824,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.02 total: parent 90.321.901,00 != sum(children) 102.983.315,00 (1 children)</t>
+          <t>51.02 total: parent 21.719.000,00 != sum(children) 325.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7848,34 +7848,34 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>total</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>unparseable cell '55.880.503 45.737.620' in column total</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -7883,97 +7883,92 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>code 10.20 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.20 total: parent 0,00 != sum(children) 26.688.357,00 (2 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.02 total: parent 21.719.000,00 != sum(children) 325.000,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>65.02 total: parent 68.779.490,00 != sum(children) 8.586.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7984,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -8033,22 +8028,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>01</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>unparseable cell '3.823.000 3.952.000' in column total</t>
         </is>
       </c>
     </row>
@@ -8064,11 +8059,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8078,64 +8073,74 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.02 total: parent 68.779.490,00 != sum(children) 8.586.000,00 (1 children)</t>
+          <t>67.02 total: parent 45.805.694,00 != sum(children) 1.932.152,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>68.02 total: parent 45.565.500,00 != sum(children) 4.151.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>70.02 total: parent 23.102.968,00 != sum(children) 3.659.360,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -8144,7 +8149,12 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -8153,7 +8163,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>unparseable cell '3.823.000 3.952.000' in column total</t>
+          <t>74.02 total: parent 22.213.388,00 != sum(children) 5.246.845,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8169,11 +8179,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8182,126 +8192,6 @@
         </is>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>67.02 total: parent 45.805.694,00 != sum(children) 1.932.152,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>68.02 total: parent 45.565.500,00 != sum(children) 4.151.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>70.02 total: parent 23.102.968,00 != sum(children) 3.659.360,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>74.02 total: parent 22.213.388,00 != sum(children) 5.246.845,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
         <is>
           <t>84.02 total: parent 63.554.395,00 != sum(children) 2.788.000,00 (2 children)</t>
         </is>
@@ -8318,7 +8208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8340,7 +8230,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8350,60 +8240,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>128</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>104</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>71f0637880d01034b4bd2734</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7fab7d85eaaf25ea969cccc246c06de996b32ad75532ced56e76d3845d4554dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL DETALIAT LA VENITURI SI CHELTUIELI PE CAPITOLE, SUBC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>unknown, pag. 1-7, 234 linii</t>
         </is>
